--- a/data/trans_camb/IP1003-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 4,2</t>
+          <t>-6,5; 4,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,79; -0,31</t>
+          <t>-10,11; -0,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 4,96</t>
+          <t>-5,96; 5,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 0,26</t>
+          <t>-8,73; 0,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 1,79</t>
+          <t>-7,79; 2,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 7,59</t>
+          <t>-6,19; 7,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,04</t>
+          <t>-5,99; 0,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,65; -0,33</t>
+          <t>-7,51; -0,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 4,78</t>
+          <t>-3,76; 4,57</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-61,74; 72,71</t>
+          <t>-59,3; 73,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,6; 3,78</t>
+          <t>-86,97; 17,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,16; 91,92</t>
+          <t>-54,0; 86,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-78,34; 10,97</t>
+          <t>-76,64; 12,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 33,67</t>
+          <t>-68,55; 49,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,09; 112,66</t>
+          <t>-54,38; 117,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,89; 16,43</t>
+          <t>-58,03; 10,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,06; -2,54</t>
+          <t>-69,86; -6,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,48; 66,42</t>
+          <t>-38,08; 66,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 0,69</t>
+          <t>-5,34; 0,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 3,88</t>
+          <t>-3,72; 3,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 6,4</t>
+          <t>-2,47; 6,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 4,85</t>
+          <t>-3,93; 4,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 3,75</t>
+          <t>-4,56; 3,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,82</t>
+          <t>-2,31; 6,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,86</t>
+          <t>-3,59; 1,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,46</t>
+          <t>-3,02; 2,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 5,24</t>
+          <t>-0,87; 4,81</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-75,93; 25,97</t>
+          <t>-73,94; 21,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,74; 110,82</t>
+          <t>-48,99; 95,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 168,42</t>
+          <t>-35,21; 164,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,76; 86,72</t>
+          <t>-41,46; 90,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,14; 66,85</t>
+          <t>-48,27; 62,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 128,17</t>
+          <t>-25,7; 126,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,26; 37,38</t>
+          <t>-46,43; 31,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 46,21</t>
+          <t>-38,06; 43,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 99,25</t>
+          <t>-11,67; 89,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 3,56</t>
+          <t>-4,01; 4,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,63</t>
+          <t>-4,88; 2,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 1,87</t>
+          <t>-4,91; 1,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,96</t>
+          <t>-5,0; 3,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,33</t>
+          <t>-6,25; 1,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 4,62</t>
+          <t>-4,58; 4,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 2,14</t>
+          <t>-3,1; 2,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 0,68</t>
+          <t>-4,33; 0,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,14</t>
+          <t>-3,48; 2,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-61,46; 124,98</t>
+          <t>-59,66; 157,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,55; 105,5</t>
+          <t>-69,86; 100,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-80,59; 69,42</t>
+          <t>-77,83; 67,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-61,4; 75,36</t>
+          <t>-60,96; 93,03</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,05; 42,12</t>
+          <t>-80,15; 39,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,57; 115,18</t>
+          <t>-58,71; 119,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-50,3; 57,01</t>
+          <t>-46,5; 65,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,39; 18,89</t>
+          <t>-65,12; 29,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 55,45</t>
+          <t>-54,37; 73,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 2,79</t>
+          <t>-4,71; 2,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,74</t>
+          <t>-4,38; 3,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 2,15</t>
+          <t>-5,1; 2,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 4,78</t>
+          <t>-3,29; 4,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,77</t>
+          <t>-4,95; 1,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 8,08</t>
+          <t>-2,01; 7,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,47</t>
+          <t>-2,94; 2,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,62</t>
+          <t>-3,74; 1,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,61</t>
+          <t>-1,99; 4,45</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,34; 92,93</t>
+          <t>-64,66; 82,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,39; 71,49</t>
+          <t>-55,41; 85,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,64; 70,01</t>
+          <t>-70,3; 75,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 128,11</t>
+          <t>-46,33; 117,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 46,49</t>
+          <t>-66,96; 47,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,17; 194,55</t>
+          <t>-29,9; 185,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 57,8</t>
+          <t>-45,32; 57,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-52,2; 36,58</t>
+          <t>-54,94; 31,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 84,25</t>
+          <t>-32,51; 100,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,77</t>
+          <t>-3,34; 0,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,41</t>
+          <t>-3,31; 0,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,78</t>
+          <t>-2,49; 1,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,33</t>
+          <t>-3,09; 1,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,33</t>
+          <t>-3,72; 0,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,77</t>
+          <t>-0,99; 3,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,47</t>
+          <t>-2,52; 0,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; -0,09</t>
+          <t>-3,1; -0,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,97</t>
+          <t>-1,23; 2,12</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 16,19</t>
+          <t>-47,17; 11,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 9,86</t>
+          <t>-47,9; 16,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 35,91</t>
+          <t>-36,19; 32,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 22,87</t>
+          <t>-38,44; 19,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,7; 4,8</t>
+          <t>-46,52; 5,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 65,54</t>
+          <t>-13,36; 66,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 8,63</t>
+          <t>-34,92; 7,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,67; -1,35</t>
+          <t>-43,33; -3,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 36,45</t>
+          <t>-16,5; 36,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1003-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 4,16</t>
+          <t>-7,28; 4,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,11; -0,26</t>
+          <t>-10,05; -0,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 5,45</t>
+          <t>-6,19; 4,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 0,57</t>
+          <t>-8,62; 0,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 2,39</t>
+          <t>-7,75; 2,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 7,29</t>
+          <t>-5,79; 7,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 0,72</t>
+          <t>-6,17; 0,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -0,81</t>
+          <t>-7,15; -0,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 4,57</t>
+          <t>-3,93; 4,46</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,3; 73,97</t>
+          <t>-62,57; 71,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,97; 17,75</t>
+          <t>-85,21; 7,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-54,0; 86,54</t>
+          <t>-52,96; 89,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-76,64; 12,78</t>
+          <t>-76,87; 15,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,55; 49,12</t>
+          <t>-71,13; 39,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,38; 117,39</t>
+          <t>-52,77; 110,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,03; 10,72</t>
+          <t>-59,64; 11,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,86; -6,99</t>
+          <t>-67,64; -3,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 66,94</t>
+          <t>-39,21; 65,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,67</t>
+          <t>-5,53; 0,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 3,78</t>
+          <t>-3,41; 3,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 6,33</t>
+          <t>-1,98; 6,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,95</t>
+          <t>-3,66; 4,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 3,32</t>
+          <t>-4,84; 3,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 6,8</t>
+          <t>-2,52; 6,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 1,66</t>
+          <t>-3,6; 1,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,4</t>
+          <t>-2,81; 2,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,81</t>
+          <t>-1,41; 4,94</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,94; 21,57</t>
+          <t>-70,93; 34,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,99; 95,04</t>
+          <t>-47,06; 95,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,21; 164,72</t>
+          <t>-26,83; 173,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 90,5</t>
+          <t>-40,75; 89,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-48,27; 62,22</t>
+          <t>-49,63; 59,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,7; 126,28</t>
+          <t>-29,81; 117,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,43; 31,83</t>
+          <t>-45,23; 34,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,06; 43,59</t>
+          <t>-36,45; 48,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 89,65</t>
+          <t>-17,58; 90,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 4,07</t>
+          <t>-3,99; 3,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 2,39</t>
+          <t>-4,63; 2,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 1,91</t>
+          <t>-5,59; 2,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,33</t>
+          <t>-5,54; 2,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,33</t>
+          <t>-6,76; 1,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 4,69</t>
+          <t>-4,64; 4,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 2,41</t>
+          <t>-3,29; 2,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,94</t>
+          <t>-4,67; 0,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,44</t>
+          <t>-4,12; 2,03</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 157,85</t>
+          <t>-61,64; 152,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 100,47</t>
+          <t>-71,01; 118,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,83; 67,31</t>
+          <t>-78,55; 94,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-60,96; 93,03</t>
+          <t>-63,87; 83,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,15; 39,67</t>
+          <t>-80,19; 32,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,71; 119,5</t>
+          <t>-61,59; 108,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 65,23</t>
+          <t>-47,62; 71,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,12; 29,08</t>
+          <t>-65,7; 24,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,37; 73,8</t>
+          <t>-57,44; 58,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 2,79</t>
+          <t>-4,84; 2,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 3,14</t>
+          <t>-4,4; 2,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 2,42</t>
+          <t>-5,32; 2,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 4,35</t>
+          <t>-3,29; 4,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 1,83</t>
+          <t>-5,08; 1,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 7,59</t>
+          <t>-1,71; 7,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,36</t>
+          <t>-3,06; 2,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,24</t>
+          <t>-3,36; 1,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,45</t>
+          <t>-2,16; 3,93</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,66; 82,61</t>
+          <t>-63,51; 83,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,41; 85,86</t>
+          <t>-60,19; 88,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,3; 75,04</t>
+          <t>-70,41; 61,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 117,59</t>
+          <t>-47,34; 114,82</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-66,96; 47,61</t>
+          <t>-67,43; 50,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 185,01</t>
+          <t>-27,09; 195,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,32; 57,84</t>
+          <t>-44,59; 54,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 31,58</t>
+          <t>-50,59; 31,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,51; 100,88</t>
+          <t>-34,75; 90,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,53</t>
+          <t>-3,36; 0,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,79</t>
+          <t>-3,49; 0,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,63</t>
+          <t>-2,58; 1,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,13</t>
+          <t>-3,0; 1,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,32</t>
+          <t>-3,9; 0,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,85</t>
+          <t>-1,11; 3,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,44</t>
+          <t>-2,45; 0,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; -0,21</t>
+          <t>-3,03; -0,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,12</t>
+          <t>-1,24; 2,08</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 11,26</t>
+          <t>-46,6; 16,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,9; 16,58</t>
+          <t>-49,28; 11,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 32,58</t>
+          <t>-36,71; 34,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 19,19</t>
+          <t>-37,68; 21,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,52; 5,85</t>
+          <t>-47,77; 5,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 66,37</t>
+          <t>-13,97; 66,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 7,84</t>
+          <t>-35,55; 7,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,33; -3,28</t>
+          <t>-42,14; -1,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 36,3</t>
+          <t>-18,33; 36,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1003-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-4,24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,93</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,28</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-5,03</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-4,24</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,93</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>-0,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 4,0</t>
+          <t>-8,98; 0,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,05; -0,35</t>
+          <t>-8,07; 1,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 4,97</t>
+          <t>-5,49; 8,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 0,32</t>
+          <t>-7,04; 4,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 2,33</t>
+          <t>-9,79; -0,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 7,23</t>
+          <t>-5,61; 5,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 0,61</t>
+          <t>-6,56; 1,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -0,41</t>
+          <t>-7,65; -0,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,46</t>
+          <t>-3,9; 5,16</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-48,11%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-33,21%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-14,91%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-58,73%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-5,76%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-48,11%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-33,21%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>-1,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-0,95%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-62,57; 71,42</t>
+          <t>-78,34; 10,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,21; 7,31</t>
+          <t>-69,32; 33,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,96; 89,38</t>
+          <t>-51,83; 126,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-76,87; 15,7</t>
+          <t>-61,74; 72,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,13; 39,28</t>
+          <t>-86,6; 3,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,77; 110,56</t>
+          <t>-51,75; 101,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,64; 11,73</t>
+          <t>-59,89; 16,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,64; -3,2</t>
+          <t>-71,06; -2,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-39,21; 65,35</t>
+          <t>-37,08; 72,73</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,49</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,76</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,03</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,05</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,89</t>
+          <t>2,43</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,05</t>
+          <t>2,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,99</t>
+          <t>-3,22; 4,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 3,5</t>
+          <t>-4,29; 3,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 6,49</t>
+          <t>-2,46; 6,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 4,8</t>
+          <t>-5,89; 0,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 3,4</t>
+          <t>-3,29; 3,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 6,77</t>
+          <t>-1,65; 6,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,71</t>
+          <t>-3,64; 1,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,52</t>
+          <t>-3,21; 2,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 4,94</t>
+          <t>-0,78; 5,34</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-6,53%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23,47%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-42,3%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-0,52%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>36,43%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-6,53%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-70,93; 34,33</t>
+          <t>-35,76; 86,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 95,94</t>
+          <t>-48,14; 66,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,83; 173,26</t>
+          <t>-28,66; 127,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,75; 89,24</t>
+          <t>-75,93; 25,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 59,9</t>
+          <t>-45,74; 110,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,81; 117,98</t>
+          <t>-24,96; 175,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 34,09</t>
+          <t>-45,26; 37,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 48,64</t>
+          <t>-40,4; 46,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,58; 90,59</t>
+          <t>-10,9; 103,94</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,45</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,51</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,08</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,45</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>-0,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,7</t>
+          <t>-4,91; 2,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 2,69</t>
+          <t>-6,56; 1,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 2,0</t>
+          <t>-3,99; 5,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 2,84</t>
+          <t>-4,11; 3,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 1,18</t>
+          <t>-4,45; 2,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 4,32</t>
+          <t>-4,71; 3,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 2,4</t>
+          <t>-3,41; 2,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,8</t>
+          <t>-4,55; 0,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 2,03</t>
+          <t>-3,03; 3,08</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-14,87%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-40,99%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-1,82%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-21,45%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-32,41%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-14,87%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-40,99%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-1,93%</t>
+          <t>-13,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-16,01%</t>
+          <t>-0,88%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-61,64; 152,58</t>
+          <t>-61,4; 75,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-71,01; 118,76</t>
+          <t>-79,05; 42,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,55; 94,28</t>
+          <t>-52,97; 141,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,87; 83,76</t>
+          <t>-61,46; 124,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,19; 32,03</t>
+          <t>-69,55; 105,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,59; 108,72</t>
+          <t>-71,72; 111,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-47,62; 71,65</t>
+          <t>-50,3; 57,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 24,4</t>
+          <t>-65,39; 18,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,44; 58,57</t>
+          <t>-46,82; 79,64</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,56</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,53</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,56</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 2,82</t>
+          <t>-3,04; 4,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,97</t>
+          <t>-4,67; 1,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 2,22</t>
+          <t>-1,81; 7,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 4,11</t>
+          <t>-4,43; 2,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,87</t>
+          <t>-4,68; 2,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 7,79</t>
+          <t>-5,01; 2,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 2,22</t>
+          <t>-2,91; 2,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,31</t>
+          <t>-3,77; 1,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 3,93</t>
+          <t>-2,29; 3,25</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-28,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>45,31%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-16,55%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-10,28%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-27,64%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-28,0%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>-24,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-63,51; 83,86</t>
+          <t>-43,07; 128,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,19; 88,31</t>
+          <t>-65,48; 46,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-70,41; 61,12</t>
+          <t>-28,62; 169,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 114,82</t>
+          <t>-62,34; 92,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,43; 50,74</t>
+          <t>-64,39; 71,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 195,57</t>
+          <t>-72,92; 78,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,59; 54,36</t>
+          <t>-43,07; 57,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 31,27</t>
+          <t>-52,2; 36,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 90,11</t>
+          <t>-33,97; 75,26</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,73</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,45</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,27</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,41</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,75</t>
+          <t>-2,86; 1,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,59</t>
+          <t>-3,59; 0,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,82</t>
+          <t>-0,9; 3,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 1,21</t>
+          <t>-3,24; 0,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,26</t>
+          <t>-3,52; 0,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,97</t>
+          <t>-2,02; 2,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,45</t>
+          <t>-2,37; 0,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; -0,11</t>
+          <t>-3,02; -0,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,08</t>
+          <t>-0,81; 2,44</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-11,71%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-25,05%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-21,26%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-23,55%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-7,61%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-11,71%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-25,05%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,6; 16,39</t>
+          <t>-36,97; 22,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,28; 11,42</t>
+          <t>-46,7; 4,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 34,74</t>
+          <t>-12,58; 68,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 21,22</t>
+          <t>-46,57; 16,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 5,43</t>
+          <t>-49,62; 9,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 66,04</t>
+          <t>-29,43; 48,49</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 7,16</t>
+          <t>-33,41; 8,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,14; -1,23</t>
+          <t>-41,67; -1,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 36,45</t>
+          <t>-11,57; 41,23</t>
         </is>
       </c>
     </row>
